--- a/LAPORAN STOK/DATA STOK KAMERA.xlsx
+++ b/LAPORAN STOK/DATA STOK KAMERA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\LAPORAN STOK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\LAPORAN STOK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D7FB8BC-0118-49F6-A881-9C83D804AC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E1A164-E9D4-431D-955A-0F81E28B4E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A8B0BE85-9D20-4728-AB63-3A1F33C5DAD9}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>Nama Barang</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Stok Awal</t>
   </si>
@@ -102,6 +99,36 @@
   </si>
   <si>
     <t>Hikvision EXID Fixed Dome H.265+</t>
+  </si>
+  <si>
+    <t>Ezviz TY1 Pro 2k</t>
+  </si>
+  <si>
+    <t>Ezviz H6c Pro 2k</t>
+  </si>
+  <si>
+    <t>Ezviz H8c 1080p</t>
+  </si>
+  <si>
+    <t>Ezviz H8c Pro 2k</t>
+  </si>
+  <si>
+    <t>Imou Ranger 2</t>
+  </si>
+  <si>
+    <t>Imou PS3E Outdoor</t>
+  </si>
+  <si>
+    <t>Imou PS8E Indoor &amp; Outdoor</t>
+  </si>
+  <si>
+    <t>Cruiser SC</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Nama barang</t>
   </si>
 </sst>
 </file>
@@ -129,15 +156,21 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -206,17 +239,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -230,6 +252,36 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -242,21 +294,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -266,14 +308,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -609,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F4F587-1884-41DC-8C6A-A0720FB29EF8}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -621,317 +674,512 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="11"/>
+      <c r="C1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="8"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>1</v>
+      <c r="A3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>0</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="6">
+        <v>29</v>
+      </c>
+      <c r="D4" s="5">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5">
+        <f>C4-D4</f>
+        <v>23</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="6">
+        <v>49</v>
+      </c>
+      <c r="D5" s="6">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" ref="E5:E28" si="0">C5-D5</f>
+        <v>43</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>3</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="5" t="s">
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="C4" s="8">
-        <v>60</v>
-      </c>
-      <c r="D4" s="9">
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4">
+        <v>7</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="9">
-        <v>49</v>
-      </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="7">
-        <v>40</v>
-      </c>
-      <c r="D5" s="10">
-        <v>6</v>
-      </c>
-      <c r="E5" s="10">
-        <v>29</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="5" t="s">
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="4">
+        <v>3</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4">
+        <v>3</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="4">
+        <v>4</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="4">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="4">
+        <v>10</v>
+      </c>
+      <c r="D22" s="14">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="4">
+        <v>14</v>
+      </c>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2</v>
+      </c>
+      <c r="D24" s="14">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="4">
+        <v>9</v>
+      </c>
+      <c r="D25" s="14">
         <v>7</v>
       </c>
-      <c r="C6" s="7">
-        <v>3</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7">
-        <v>3</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="5" t="s">
+      <c r="E25" s="5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="4">
         <v>8</v>
       </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="D26" s="14">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="4">
+        <v>7</v>
+      </c>
+      <c r="D27" s="14">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="6">
         <v>4</v>
       </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7">
+      <c r="D28" s="14">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="7">
-        <v>7</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7">
-        <v>7</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="10">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="7">
-        <v>2</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2</v>
-      </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="7">
-        <v>3</v>
-      </c>
-      <c r="D14" s="10">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7">
-        <v>3</v>
-      </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="7">
-        <v>3</v>
-      </c>
-      <c r="D15" s="10">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3</v>
-      </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1</v>
-      </c>
-      <c r="D16" s="10">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="7">
-        <v>4</v>
-      </c>
-      <c r="D17" s="10">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7">
-        <v>4</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="7">
-        <v>2</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2</v>
-      </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="7">
-        <v>2</v>
-      </c>
-      <c r="D19" s="10">
-        <v>0</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2</v>
-      </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="7">
-        <v>1</v>
-      </c>
-      <c r="D20" s="10">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1</v>
-      </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/LAPORAN STOK/DATA STOK KAMERA.xlsx
+++ b/LAPORAN STOK/DATA STOK KAMERA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\LAPORAN STOK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E1A164-E9D4-431D-955A-0F81E28B4E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4368BC51-F170-4401-82C9-429B179222CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A8B0BE85-9D20-4728-AB63-3A1F33C5DAD9}"/>
   </bookViews>
